--- a/fund_manager_control.xlsx
+++ b/fund_manager_control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/375bf9a97ade46a2/Desktop/BFIN491/BFIN491project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baileybinando/Desktop/BFIN491/BFIN491project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_DFB4FEF689284CC209A93C4F05E4F42B70745AF5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0E81528-84F6-4636-9706-7A88E314FC6E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABE52DE-B651-3B42-9E9D-53F959C9EA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1200" windowWidth="24500" windowHeight="13780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="288">
   <si>
     <t>Fund Management Dashboard Capstone — Control Workbook</t>
   </si>
@@ -874,6 +874,21 @@
   </si>
   <si>
     <t>InheritedFund!A43</t>
+  </si>
+  <si>
+    <t>InheritedFund!A51</t>
+  </si>
+  <si>
+    <t>InheritedFund!A59</t>
+  </si>
+  <si>
+    <t>InheritedFund!A67</t>
+  </si>
+  <si>
+    <t>InheritedFund!A75</t>
+  </si>
+  <si>
+    <t>InheritedFund!A83</t>
   </si>
 </sst>
 </file>
@@ -1107,12 +1122,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1564,6 +1579,377 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47049</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>14652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1792897</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>120753</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD211A2-D9B8-CA46-9954-A1B7DC01116D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47049" y="10267256"/>
+          <a:ext cx="4788556" cy="1336414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>KO had an annualized</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> return of 10.2%, a volatility of 14.8%, and a max drawdown of -13.6%, underperforming compared to the other stocks but reports strong stability.  The correlation coefficient of 0.56 indicates the stock provides diversification to the portfolio, but this effect is minimized by the low ending weight. Seen in the Individual Stock Returns vs. SPY Chart, KO underperforms SPY. The stock was moved to the DROP stocks due to the declining portfolio weight and lower return.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>40435</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>11461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1786283</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>117563</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02E06E2-F08D-8F44-9962-0853F4641474}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40435" y="11904482"/>
+          <a:ext cx="4788556" cy="1336414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>MSFT reported an annualized return of 20.6%,  a beta of 1.07, and a sharpe ratio of 0.91. Despite the high dependency on SPY (0.69), the stock had strong performance and </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>risk-adjusted returns. The stock was placed in KEEP, because of the high performance and stability alongside its growth, seen in the max drawdown of -26.4%.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>46486</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>4966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1792334</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>113460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A61CDFA5-7886-E34F-A9C5-516B5DAFBF35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="46486" y="13538404"/>
+          <a:ext cx="4788556" cy="1338806"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>ORCL ended with a sharpe ratio of 0.4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> and 23.3% annualized volatility. Despite a high dependency (0.68) and elevated market risk (beta = 1.08), the stock was unable to capitalize with an annualized return of 9.3%, underperforming to the SPY. The ending weight of 4.4% supports the categorization of DROP. </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>40152</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>10171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1786000</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>116273</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91AE5A26-FB62-174B-951E-66B014283453}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40152" y="15184025"/>
+          <a:ext cx="4788556" cy="1336415"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>WFC had</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> the highest correlation to SPY (0.75), with a low sharpe ratio of 0.41 and an annualized return of 9.9%. This stock fails to meet the necessary benchmarks with the weak risk-adjusted performance and high market correlation. The high volatility (beta = 1.23) in combination with these other factors places WFC in the DROP category.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47049</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>203847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1792897</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>104896</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{131C50F6-422E-CD44-8EDB-B9654593389B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47049" y="16813066"/>
+          <a:ext cx="4788556" cy="1336413"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>XOM maintained the lowest</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> annualized return (3.4%) of all the stocks, with a beta of 0.92 and a correlation of 0.72. The limited diversification, poor performance, and high maxdropdown (-31.5%) places this stock in the DROP section. Despite a moderate beta, the stock greatly underperformed compared to the market and adds little value to the portfolio.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1885,21 +2271,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35.796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.69921875" style="2" customWidth="1"/>
-    <col min="4" max="6" width="10.796875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.796875" style="2"/>
+    <col min="1" max="1" width="58.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="10.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1910,7 +2296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1921,7 +2307,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1932,7 +2318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1943,7 +2329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1954,7 +2340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -1965,7 +2351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1976,7 +2362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -1987,7 +2373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1998,7 +2384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -2009,7 +2395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -2020,7 +2406,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -2050,18 +2436,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:I13"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20" style="2" customWidth="1"/>
     <col min="3" max="3" width="24" style="2" customWidth="1"/>
     <col min="4" max="4" width="20" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="12" width="10.796875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="10.796875" style="2"/>
+    <col min="10" max="12" width="10.83203125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -2090,7 +2476,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -2109,11 +2495,11 @@
       <c r="F4" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="31" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -2132,11 +2518,11 @@
       <c r="F5" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="31" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -2155,11 +2541,11 @@
       <c r="F6" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="31" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -2178,11 +2564,11 @@
       <c r="F7" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="31" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
@@ -2201,11 +2587,11 @@
       <c r="F8" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="31" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>52</v>
       </c>
@@ -2221,8 +2607,14 @@
       <c r="E9" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>55</v>
       </c>
@@ -2238,8 +2630,14 @@
       <c r="E10" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F10" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
@@ -2255,8 +2653,14 @@
       <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
@@ -2272,8 +2676,14 @@
       <c r="E12" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F12" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
@@ -2288,6 +2698,12 @@
       </c>
       <c r="E13" s="2" t="s">
         <v>63</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -2305,6 +2721,11 @@
     <hyperlink ref="I6" location="InheritedFund!A30" display="InheritedFund!A30" xr:uid="{0C1FF6CD-01E8-46CD-A96D-80851981ED3E}"/>
     <hyperlink ref="I7" location="InheritedFund!A36" display="InheritedFund!A36" xr:uid="{5A18B8F3-6AEB-4F38-A69B-544EF27629F4}"/>
     <hyperlink ref="I8" location="InheritedFund!A43" display="InheritedFund!A43" xr:uid="{9626A3B2-4E83-4D21-BCEC-55366B914CAA}"/>
+    <hyperlink ref="I9" location="InheritedFund!A51" display="InheritedFund!A51" xr:uid="{0B38C197-6315-154A-A920-15F37F8A4B62}"/>
+    <hyperlink ref="I10" location="InheritedFund!A59" display="InheritedFund!A59" xr:uid="{DF2591B6-07A8-0446-A168-BE6674EFE3C4}"/>
+    <hyperlink ref="I11" location="InheritedFund!A67" display="InheritedFund!A67" xr:uid="{7B77F7CD-59EE-F94D-A3FD-FED6F629C1B7}"/>
+    <hyperlink ref="I12" location="InheritedFund!A75" display="InheritedFund!A75" xr:uid="{8A126E5D-40AD-7742-8131-0C2169383BB5}"/>
+    <hyperlink ref="I13" location="InheritedFund!A83" display="InheritedFund!A83" xr:uid="{35F85D7A-8718-4649-A48B-B45EAE27213F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2314,14 +2735,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:J28"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="10" width="20" style="2" customWidth="1"/>
-    <col min="11" max="13" width="10.796875" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="10.796875" style="2"/>
+    <col min="11" max="13" width="10.83203125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
@@ -2353,127 +2774,127 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -2494,16 +2915,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:C14"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.69921875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.19921875" style="2" customWidth="1"/>
-    <col min="4" max="6" width="10.796875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.796875" style="2"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="10.83203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2514,7 +2935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -2525,7 +2946,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>97</v>
       </c>
@@ -2536,7 +2957,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>98</v>
       </c>
@@ -2547,7 +2968,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -2558,7 +2979,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -2569,7 +2990,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>103</v>
       </c>
@@ -2580,7 +3001,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>104</v>
       </c>
@@ -2591,7 +3012,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>105</v>
       </c>
@@ -2602,7 +3023,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>106</v>
       </c>
@@ -2613,7 +3034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -2624,7 +3045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -2643,7 +3064,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I100"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="2" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2655,12 +3076,12 @@
     <col min="12" max="16384" width="14" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -2668,7 +3089,7 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>113</v>
       </c>
@@ -2685,7 +3106,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>114</v>
       </c>
@@ -2702,7 +3123,7 @@
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>117</v>
       </c>
@@ -2719,7 +3140,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>119</v>
       </c>
@@ -2736,7 +3157,7 @@
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
     </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>121</v>
       </c>
@@ -2753,7 +3174,7 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
     </row>
-    <row r="7" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>123</v>
       </c>
@@ -2770,20 +3191,20 @@
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
     </row>
-    <row r="8" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>126</v>
       </c>
@@ -2808,7 +3229,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>27</v>
       </c>
@@ -2833,7 +3254,7 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>41</v>
       </c>
@@ -2858,7 +3279,7 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>44</v>
       </c>
@@ -2883,7 +3304,7 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>47</v>
       </c>
@@ -2908,7 +3329,7 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>50</v>
       </c>
@@ -2933,7 +3354,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>52</v>
       </c>
@@ -2958,7 +3379,7 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>55</v>
       </c>
@@ -2983,7 +3404,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
     </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
         <v>57</v>
       </c>
@@ -3008,7 +3429,7 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>59</v>
       </c>
@@ -3033,7 +3454,7 @@
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
     </row>
-    <row r="19" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>61</v>
       </c>
@@ -3058,7 +3479,7 @@
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -3069,20 +3490,20 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
     </row>
-    <row r="21" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+    <row r="21" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-    </row>
-    <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+    </row>
+    <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>136</v>
       </c>
@@ -3111,7 +3532,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>145</v>
       </c>
@@ -3140,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>146</v>
       </c>
@@ -3153,7 +3574,7 @@
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
     </row>
-    <row r="25" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>147</v>
       </c>
@@ -3166,7 +3587,7 @@
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
     </row>
-    <row r="26" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>148</v>
       </c>
@@ -3195,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -3206,7 +3627,7 @@
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -3217,12 +3638,12 @@
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
+    <row r="29" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -3230,7 +3651,7 @@
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>113</v>
       </c>
@@ -3247,7 +3668,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>106</v>
       </c>
@@ -3264,7 +3685,7 @@
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
     </row>
-    <row r="32" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>98</v>
       </c>
@@ -3281,7 +3702,7 @@
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
     </row>
-    <row r="33" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>100</v>
       </c>
@@ -3298,7 +3719,7 @@
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>104</v>
       </c>
@@ -3315,7 +3736,7 @@
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>105</v>
       </c>
@@ -3332,7 +3753,7 @@
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
     </row>
-    <row r="36" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>155</v>
       </c>
@@ -3349,7 +3770,7 @@
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
     </row>
-    <row r="37" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>158</v>
       </c>
@@ -3366,20 +3787,20 @@
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>136</v>
       </c>
@@ -3404,7 +3825,7 @@
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="16" t="s">
         <v>145</v>
       </c>
@@ -3429,7 +3850,7 @@
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
     </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="16"/>
       <c r="B41" s="17"/>
       <c r="C41" s="21"/>
@@ -3440,7 +3861,7 @@
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
     </row>
-    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="16"/>
       <c r="B42" s="17"/>
       <c r="C42" s="21"/>
@@ -3451,7 +3872,7 @@
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
     </row>
-    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="16"/>
       <c r="B43" s="17"/>
       <c r="C43" s="21"/>
@@ -3462,7 +3883,7 @@
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
     </row>
-    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -3473,20 +3894,20 @@
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
     </row>
-    <row r="45" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
+    <row r="45" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>136</v>
       </c>
@@ -3513,7 +3934,7 @@
       </c>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="16" t="s">
         <v>146</v>
       </c>
@@ -3528,7 +3949,7 @@
       </c>
       <c r="I47" s="14"/>
     </row>
-    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="16" t="s">
         <v>147</v>
       </c>
@@ -3543,7 +3964,7 @@
       </c>
       <c r="I48" s="14"/>
     </row>
-    <row r="49" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="16"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -3554,7 +3975,7 @@
       <c r="H49" s="18"/>
       <c r="I49" s="14"/>
     </row>
-    <row r="50" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="16"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -3565,7 +3986,7 @@
       <c r="H50" s="18"/>
       <c r="I50" s="14"/>
     </row>
-    <row r="51" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -3576,7 +3997,7 @@
       <c r="H51" s="18"/>
       <c r="I51" s="14"/>
     </row>
-    <row r="52" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="16"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -3587,7 +4008,7 @@
       <c r="H52" s="18"/>
       <c r="I52" s="14"/>
     </row>
-    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="14"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -3598,12 +4019,12 @@
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
     </row>
-    <row r="54" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="31" t="s">
+    <row r="54" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -3611,7 +4032,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
         <v>177</v>
       </c>
@@ -3628,7 +4049,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="16" t="s">
         <v>180</v>
       </c>
@@ -3645,7 +4066,7 @@
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
     </row>
-    <row r="57" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="16" t="s">
         <v>180</v>
       </c>
@@ -3662,7 +4083,7 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
     </row>
-    <row r="58" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="16" t="s">
         <v>180</v>
       </c>
@@ -3679,7 +4100,7 @@
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
     </row>
-    <row r="59" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="16" t="s">
         <v>180</v>
       </c>
@@ -3696,7 +4117,7 @@
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
     </row>
-    <row r="60" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="16" t="s">
         <v>180</v>
       </c>
@@ -3713,7 +4134,7 @@
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
     </row>
-    <row r="61" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="16" t="s">
         <v>180</v>
       </c>
@@ -3730,7 +4151,7 @@
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
     </row>
-    <row r="62" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
         <v>180</v>
       </c>
@@ -3747,7 +4168,7 @@
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
     </row>
-    <row r="63" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
         <v>180</v>
       </c>
@@ -3764,7 +4185,7 @@
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
     </row>
-    <row r="64" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
         <v>197</v>
       </c>
@@ -3781,7 +4202,7 @@
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
     </row>
-    <row r="65" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
         <v>197</v>
       </c>
@@ -3798,7 +4219,7 @@
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
     </row>
-    <row r="66" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
         <v>197</v>
       </c>
@@ -3815,7 +4236,7 @@
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
     </row>
-    <row r="67" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="16" t="s">
         <v>197</v>
       </c>
@@ -3832,7 +4253,7 @@
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
     </row>
-    <row r="68" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="16" t="s">
         <v>197</v>
       </c>
@@ -3849,7 +4270,7 @@
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
     </row>
-    <row r="69" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="16" t="s">
         <v>197</v>
       </c>
@@ -3866,7 +4287,7 @@
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
     </row>
-    <row r="70" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16"/>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
@@ -3877,7 +4298,7 @@
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
     </row>
-    <row r="71" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16"/>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -3888,7 +4309,7 @@
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
     </row>
-    <row r="72" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -3899,7 +4320,7 @@
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
     </row>
-    <row r="73" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -3910,7 +4331,7 @@
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
     </row>
-    <row r="74" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -3921,7 +4342,7 @@
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
     </row>
-    <row r="75" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
@@ -3932,7 +4353,7 @@
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
@@ -3943,7 +4364,7 @@
       <c r="H76" s="27"/>
       <c r="I76" s="27"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
@@ -3954,7 +4375,7 @@
       <c r="H77" s="27"/>
       <c r="I77" s="27"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="27"/>
       <c r="B78" s="27"/>
       <c r="C78" s="27"/>
@@ -3965,7 +4386,7 @@
       <c r="H78" s="27"/>
       <c r="I78" s="27"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="27"/>
       <c r="B79" s="27"/>
       <c r="C79" s="27"/>
@@ -3976,7 +4397,7 @@
       <c r="H79" s="27"/>
       <c r="I79" s="27"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="27"/>
       <c r="B80" s="27"/>
       <c r="C80" s="27"/>
@@ -3987,7 +4408,7 @@
       <c r="H80" s="27"/>
       <c r="I80" s="27"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="27"/>
       <c r="B81" s="27"/>
       <c r="C81" s="27"/>
@@ -3998,7 +4419,7 @@
       <c r="H81" s="27"/>
       <c r="I81" s="27"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="27"/>
       <c r="B82" s="27"/>
       <c r="C82" s="27"/>
@@ -4009,7 +4430,7 @@
       <c r="H82" s="27"/>
       <c r="I82" s="27"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="27"/>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -4020,7 +4441,7 @@
       <c r="H83" s="27"/>
       <c r="I83" s="27"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="27"/>
       <c r="B84" s="27"/>
       <c r="C84" s="27"/>
@@ -4031,7 +4452,7 @@
       <c r="H84" s="27"/>
       <c r="I84" s="27"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="27"/>
       <c r="B85" s="27"/>
       <c r="C85" s="27"/>
@@ -4042,7 +4463,7 @@
       <c r="H85" s="27"/>
       <c r="I85" s="27"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="27"/>
       <c r="B86" s="27"/>
       <c r="C86" s="27"/>
@@ -4053,7 +4474,7 @@
       <c r="H86" s="27"/>
       <c r="I86" s="27"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="27"/>
       <c r="B87" s="27"/>
       <c r="C87" s="27"/>
@@ -4064,7 +4485,7 @@
       <c r="H87" s="27"/>
       <c r="I87" s="27"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="27"/>
       <c r="B88" s="27"/>
       <c r="C88" s="27"/>
@@ -4075,7 +4496,7 @@
       <c r="H88" s="27"/>
       <c r="I88" s="27"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="27"/>
       <c r="B89" s="27"/>
       <c r="C89" s="27"/>
@@ -4086,7 +4507,7 @@
       <c r="H89" s="27"/>
       <c r="I89" s="27"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="27"/>
       <c r="B90" s="27"/>
       <c r="C90" s="27"/>
@@ -4097,7 +4518,7 @@
       <c r="H90" s="27"/>
       <c r="I90" s="27"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="27"/>
       <c r="B91" s="27"/>
       <c r="C91" s="27"/>
@@ -4108,7 +4529,7 @@
       <c r="H91" s="27"/>
       <c r="I91" s="27"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="27"/>
       <c r="B92" s="27"/>
       <c r="C92" s="27"/>
@@ -4119,7 +4540,7 @@
       <c r="H92" s="27"/>
       <c r="I92" s="27"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="27"/>
       <c r="B93" s="27"/>
       <c r="C93" s="27"/>
@@ -4130,7 +4551,7 @@
       <c r="H93" s="27"/>
       <c r="I93" s="27"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="27"/>
       <c r="B94" s="27"/>
       <c r="C94" s="27"/>
@@ -4141,7 +4562,7 @@
       <c r="H94" s="27"/>
       <c r="I94" s="27"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="27"/>
       <c r="B95" s="27"/>
       <c r="C95" s="27"/>
@@ -4152,7 +4573,7 @@
       <c r="H95" s="27"/>
       <c r="I95" s="27"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="27"/>
       <c r="B96" s="27"/>
       <c r="C96" s="27"/>
@@ -4163,7 +4584,7 @@
       <c r="H96" s="27"/>
       <c r="I96" s="27"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="27"/>
       <c r="B97" s="27"/>
       <c r="C97" s="27"/>
@@ -4174,7 +4595,7 @@
       <c r="H97" s="27"/>
       <c r="I97" s="27"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="27"/>
       <c r="B98" s="27"/>
       <c r="C98" s="27"/>
@@ -4185,7 +4606,7 @@
       <c r="H98" s="27"/>
       <c r="I98" s="27"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="27"/>
       <c r="B99" s="27"/>
       <c r="C99" s="27"/>
@@ -4196,7 +4617,7 @@
       <c r="H99" s="27"/>
       <c r="I99" s="27"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="27"/>
       <c r="B100" s="27"/>
       <c r="C100" s="27"/>
@@ -4224,7 +4645,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" style="2" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" customWidth="1"/>
@@ -4232,21 +4653,21 @@
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="9" width="10.796875" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="10.796875" style="2"/>
+    <col min="7" max="9" width="10.83203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
         <v>211</v>
       </c>
@@ -4258,7 +4679,7 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>213</v>
       </c>
@@ -4266,19 +4687,19 @@
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>215</v>
       </c>
       <c r="B5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>216</v>
       </c>
       <c r="B6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="28" t="s">
         <v>217</v>
       </c>
@@ -4298,7 +4719,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -4315,7 +4736,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -4332,7 +4753,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>115</v>
       </c>
@@ -4349,7 +4770,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>115</v>
       </c>
@@ -4366,7 +4787,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>115</v>
       </c>
@@ -4383,7 +4804,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -4400,7 +4821,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -4417,7 +4838,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -4434,7 +4855,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>115</v>
       </c>
@@ -4451,7 +4872,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -4468,7 +4889,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -4485,7 +4906,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -4502,7 +4923,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>115</v>
       </c>
@@ -4519,7 +4940,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -4536,7 +4957,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>115</v>
       </c>
@@ -4553,7 +4974,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>115</v>
       </c>
@@ -4570,7 +4991,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -4587,7 +5008,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>115</v>
       </c>
@@ -4604,7 +5025,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -4621,7 +5042,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -4638,7 +5059,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -4655,7 +5076,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>115</v>
       </c>
@@ -4672,7 +5093,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>115</v>
       </c>
@@ -4689,7 +5110,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -4706,7 +5127,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -4723,7 +5144,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>115</v>
       </c>
@@ -4740,7 +5161,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>115</v>
       </c>
@@ -4757,7 +5178,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -4774,7 +5195,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>115</v>
       </c>
@@ -4791,7 +5212,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>115</v>
       </c>
@@ -4808,7 +5229,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>115</v>
       </c>
@@ -4825,7 +5246,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -4842,7 +5263,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>115</v>
       </c>
@@ -4859,7 +5280,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>115</v>
       </c>
@@ -4876,7 +5297,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -4893,7 +5314,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>115</v>
       </c>
@@ -4910,7 +5331,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>115</v>
       </c>
@@ -4927,7 +5348,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -4944,7 +5365,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>115</v>
       </c>
@@ -4961,7 +5382,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>115</v>
       </c>
@@ -4978,7 +5399,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>115</v>
       </c>

--- a/fund_manager_control.xlsx
+++ b/fund_manager_control.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InheritedFund" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constraints" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes_Manifest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="InheritedFund" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Candidates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Constraints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Outputs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Notes_Manifest" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -150,7 +150,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,6 +234,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -643,8 +644,8 @@
     <col width="58.33203125" customWidth="1" style="2" min="1" max="1"/>
     <col width="35.83203125" customWidth="1" style="2" min="2" max="2"/>
     <col width="26.6640625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="10.83203125" customWidth="1" style="2" min="6" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="4" max="9"/>
+    <col width="10.83203125" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,8 +887,8 @@
     <col width="20" customWidth="1" style="2" min="4" max="4"/>
     <col width="21.1640625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="20" customWidth="1" style="2" min="6" max="9"/>
-    <col width="10.83203125" customWidth="1" style="2" min="10" max="11"/>
-    <col width="10.83203125" customWidth="1" style="2" min="12" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="10" max="15"/>
+    <col width="10.83203125" customWidth="1" style="2" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -961,6 +962,19 @@
           <t>Technology</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -986,6 +1000,19 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1011,6 +1038,19 @@
           <t>Financials</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1036,6 +1076,19 @@
           <t>Communication Services</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1061,6 +1114,19 @@
           <t>Communication Services</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1086,6 +1152,19 @@
           <t>Consumer Staples</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1111,6 +1190,19 @@
           <t>Technology</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1136,6 +1228,19 @@
           <t>Technology</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1161,6 +1266,19 @@
           <t>Financials</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1185,6 +1303,19 @@
         <is>
           <t>Energy</t>
         </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1337,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:J28"/>
+  <dimension ref="A3:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="20" customWidth="1" style="2" min="1" max="10"/>
-    <col width="10.83203125" customWidth="1" style="2" min="11" max="12"/>
-    <col width="10.83203125" customWidth="1" style="2" min="13" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="11" max="16"/>
+    <col width="10.83203125" customWidth="1" style="2" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1269,175 +1400,750 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Financials / Payments</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Global cashless payment network with near-monopoly economics; secular shift from cash to digital payments</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; network effect moat; best-in-class by 5yr EPS growth and network volume ($8.8T processed in 2019)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Selected: largest global payment network, highest EPS growth in sector</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Financials / Payments</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Second-largest global payment network with economics nearly identical to Visa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; network effect moat; rejected by best-in-class sub-rule — V processed $8.8T vs MA $6.5T in 2019; larger network wins</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rejected: passes all rules but loses best-in-class to V on network volume and EPS growth</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Financials / Payments</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Largest U.S. bank by assets with diversified financial services across retail, investment banking, and asset management</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Passes size and profitability screens; strong moat; rejected — traditional banking adds credit-cycle and regulatory risk; prefer pure-play payment network for 30-40yr horizon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rejected: moat present but banking model adds macro sensitivity inconsistent with fund mandate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DDD</t>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Walmart Inc.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recession-proof retailer with cost-advantage moat and active e-commerce pivot underway as of Jan 2020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; cost advantage + brand moat; best-in-class by global scale, revenue size, and 40+ yr dividend growth track record</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Selected: largest global retailer, superior scale moat, longest dividend growth streak in sector</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Corporation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Membership-model warehouse retailer with exceptional customer loyalty and high annual renewal rates (~90%)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; membership moat is strong; rejected by best-in-class sub-rule — WMT has larger global footprint and longer dividend growth history</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Rejected: strong candidate but loses best-in-class to WMT on scale and dividend track record</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FFF</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Target Corporation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mid-size U.S. retailer with strong private-label brands and improving same-store sales momentum entering 2020</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fails size screen — market cap ~$44B in Jan 2020, below $50B threshold; eliminated at first filter before reaching moat or growth analysis</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Rejected: fails Rule 1 (size) — market cap below $50B minimum as of Jan 2020</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GGG</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chevron Corporation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Best-balance-sheet integrated oil major; oil demand on 2020 consensus was decades from structural peak</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; regulatory license + scale moat; best-in-class vs. XOM on D/E ratio and credit strength; lower financial risk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Selected: integrated major with superior balance sheet; best-in-class by debt-to-equity vs. XOM</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HHH</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Largest U.S. integrated oil major; held in legacy inherited fund before manager takeover</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Passes size and profitability screens; regulatory license moat; rejected by best-in-class sub-rule — higher D/E ratio and weaker balance sheet than CVX as of Jan 2020</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Rejected: passes all rules but loses best-in-class to CVX on balance sheet strength</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>III</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ConocoPhillips</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Large U.S. exploration and production company focused solely on upstream oil and gas</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Passes size screen; fails moat screen — E&amp;P-only model has no downstream diversification, making returns more directly tied to spot commodity prices with no margin buffer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Rejected: fails Rule 3 (moat) — no integrated buffer; commodity price exposure too high for retirement mandate</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>KKK</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NextEra Energy Inc.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Regulated Florida utility monopoly and worlds largest wind/solar operator; rare utility with 8-10% 5yr EPS CAGR as of 2020</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; regulatory license moat; best-in-class by 5yr EPS CAGR (8-10% vs. 2-3% for DUK/SO/AEP); lowest coal exposure</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Selected: only utility combining regulated monopoly moat with meaningful EPS growth; renewable secular tailwind</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>LLL</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DUK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DUK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Duke Energy Corporation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Large regulated utility serving 7.7M customers across the Southeast and Midwest U.S.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Passes size and profitability screens; regulatory license moat; rejected by best-in-class sub-rule — 5yr EPS CAGR ~2-3% vs NEE 8-10%; heavy coal generation fleet limits long-horizon growth</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Rejected: passes all rules but loses best-in-class to NEE on EPS growth and renewable positioning</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>MMM</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Southern Company</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Regulated utility serving the Southeast with a long dividend history and stable regulated earnings</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Passes size and profitability screens; regulatory license moat; rejected by best-in-class sub-rule — similar low EPS growth to DUK; slow renewable transition relative to NEE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Rejected: passes all rules but loses best-in-class to NEE on EPS growth rate and forward-looking energy mix</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>NNN</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Inc.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Largest U.S. health insurer plus Optum data and pharmacy arm; aging demographics provide 30-40yr secular tailwind</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; switching cost + network moat; best-in-class by 5yr EPS CAGR (~15%+ vs. peers at 6-8%); investment-grade balance sheet</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Selected: highest EPS growth in healthcare; switching cost moat from employer contracts; Optum diversification</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>OOO</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Diversified healthcare conglomerate spanning pharmaceuticals, medical devices, and consumer products</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Passes all 4 screens; brand + IP moat is strong; rejected by best-in-class sub-rule — 5yr EPS CAGR ~6-8% vs UNH 15%+; also facing active talc litigation headwinds as of Jan 2020</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rejected: strong moat but lower EPS growth; litigation risk adds uncertainty inconsistent with retirement mandate</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>PPP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>RRR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TTT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>UUU</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>VVV</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>WWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>XXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>YYY</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ZZZ</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Integrated pharmacy and insurance company following the 2018 Aetna acquisition</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Passes size and profitability screens; moderate switching cost moat; rejected — elevated D/E ratio from Aetna acquisition (2018) disqualifies under investment-grade requirement of best-in-class sub-rule</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Rejected: fails best-in-class sub-rule on balance sheet — Aetna debt load elevated D/E above acceptable threshold</t>
         </is>
       </c>
     </row>
@@ -1466,8 +2172,8 @@
     <col width="26.6640625" customWidth="1" style="2" min="1" max="1"/>
     <col width="15" customWidth="1" style="7" min="2" max="2"/>
     <col width="19.1640625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="10.83203125" customWidth="1" style="2" min="6" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="4" max="9"/>
+    <col width="10.83203125" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1617,7 +2323,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>equal_weight</t>
+          <t>optimizer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1678,18 +2384,18 @@
     <col width="18" customWidth="1" min="4" max="6"/>
     <col width="28" customWidth="1" style="2" min="7" max="7"/>
     <col width="24" customWidth="1" style="2" min="8" max="8"/>
-    <col width="14" customWidth="1" style="2" min="9" max="10"/>
-    <col width="14" customWidth="1" style="2" min="11" max="16384"/>
+    <col width="14" customWidth="1" style="2" min="9" max="14"/>
+    <col width="14" customWidth="1" style="2" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Run Status</t>
         </is>
       </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
+      <c r="B1" s="33" t="n"/>
+      <c r="C1" s="33" t="n"/>
       <c r="D1" s="8" t="n"/>
       <c r="E1" s="8" t="n"/>
       <c r="F1" s="8" t="n"/>
@@ -1728,7 +2434,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -1774,7 +2480,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>OK: required sheets, parameters, columns, and price-panel quality checks were validated. Warnings: 1</t>
+          <t>OK: required sheets, parameters, columns, and price-panel quality checks were validated.</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -1797,7 +2503,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: inherited-fund and candidate-screen outputs are ready; revised-static and revised-active are still pending.</t>
+          <t>YES: inherited-fund, candidate-screen, revised-static, revised-active, factor/regression, and scenario/stress CSVs/figures were exported successfully.</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1836,17 +2542,17 @@
       <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Final Portfolio Snapshot</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
     </row>
@@ -1902,7 +2608,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -1911,16 +2617,12 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>Starter default: legacy equal-weight fund.</t>
-        </is>
-      </c>
+        <v>0.1471274389793825</v>
+      </c>
+      <c r="G10" s="18" t="inlineStr"/>
       <c r="H10" s="14" t="n"/>
       <c r="I10" s="14" t="n"/>
     </row>
@@ -1937,7 +2639,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -1946,23 +2648,19 @@
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>Starter default: legacy equal-weight fund.</t>
-        </is>
-      </c>
+        <v>0.1508812989850544</v>
+      </c>
+      <c r="G11" s="18" t="inlineStr"/>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -1972,7 +2670,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -1984,20 +2682,16 @@
         <v>0.1</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>Starter default: legacy equal-weight fund.</t>
-        </is>
-      </c>
+        <v>0.106404989268606</v>
+      </c>
+      <c r="G12" s="18" t="inlineStr"/>
       <c r="H12" s="14" t="n"/>
       <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -2007,7 +2701,7 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -2019,20 +2713,16 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>Starter default: legacy equal-weight fund.</t>
-        </is>
-      </c>
+        <v>0.1017972584376416</v>
+      </c>
+      <c r="G13" s="18" t="inlineStr"/>
       <c r="H13" s="14" t="n"/>
       <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -2042,7 +2732,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -2054,30 +2744,26 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>Starter default: legacy equal-weight fund.</t>
-        </is>
-      </c>
+        <v>0.1000609001022294</v>
+      </c>
+      <c r="G14" s="18" t="inlineStr"/>
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -2086,14 +2772,14 @@
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08457226388181856</v>
       </c>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>Starter default: legacy equal-weight fund.</t>
+          <t>Selected: largest global payment network, highest EPS growth in sector</t>
         </is>
       </c>
       <c r="H15" s="14" t="n"/>
@@ -2102,17 +2788,17 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -2121,14 +2807,14 @@
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08393035349059123</v>
       </c>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>Starter default: legacy equal-weight fund.</t>
+          <t>Selected: largest global retailer, superior scale moat, longest dividend growth streak in sector</t>
         </is>
       </c>
       <c r="H16" s="14" t="n"/>
@@ -2137,17 +2823,17 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -2156,14 +2842,14 @@
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07665445186007529</v>
       </c>
       <c r="G17" s="18" t="inlineStr">
         <is>
-          <t>Starter default: legacy equal-weight fund.</t>
+          <t>Selected: integrated major with superior balance sheet; best-in-class by debt-to-equity vs. XOM</t>
         </is>
       </c>
       <c r="H17" s="14" t="n"/>
@@ -2172,17 +2858,17 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -2191,14 +2877,14 @@
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07197041622530083</v>
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
-          <t>Starter default: legacy equal-weight fund.</t>
+          <t>Selected: only utility combining regulated monopoly moat with meaningful EPS growth; renewable secular tailwind</t>
         </is>
       </c>
       <c r="H18" s="14" t="n"/>
@@ -2207,17 +2893,17 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Legacy hold</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
@@ -2226,14 +2912,14 @@
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07660062876930029</v>
       </c>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>Starter default: legacy equal-weight fund.</t>
+          <t>Selected: highest EPS growth in healthcare; switching cost moat from employer contracts; Optum diversification</t>
         </is>
       </c>
       <c r="H19" s="14" t="n"/>
@@ -2251,19 +2937,19 @@
       <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Top-Level Performance Summary</t>
         </is>
       </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="33" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2319,25 +3005,25 @@
         </is>
       </c>
       <c r="B23" s="20" t="n">
-        <v>15261597.03215112</v>
+        <v>15261596.96739008</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1.75709488454291</v>
+        <v>1.757094603014801</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>0.1846862191688263</v>
+        <v>0.1846861989538795</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.2432814255138178</v>
+        <v>0.2432813945947335</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.7591464033012936</v>
+        <v>0.75914641668976</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>1.002197819259307</v>
+        <v>1.002197876885282</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>-0.3137782372352629</v>
+        <v>-0.3137782669699901</v>
       </c>
       <c r="I23" s="17" t="n">
         <v>0</v>
@@ -2349,14 +3035,30 @@
           <t>Revised Static Fund</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
+      <c r="B24" s="20" t="n">
+        <v>14048737.59742697</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>1.537984635015615</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0.168405655926855</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.2190818660371811</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>0.76868824870368</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>0.9819216569586509</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>-0.273907482893831</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -2364,14 +3066,30 @@
           <t>Revised Active Fund</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
+      <c r="B25" s="20" t="n">
+        <v>14100074.20713302</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>1.547258886580511</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0.1691180541192125</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.2133341758305466</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0.7927377479993858</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>1.004152961658763</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>-0.27829229113173</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>0.02146566493433784</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -2380,25 +3098,25 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>12679565.90321468</v>
+        <v>12679565.84077461</v>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1.290636177611785</v>
+        <v>1.290635942153882</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>0.1485550554107495</v>
+        <v>0.1485550356816079</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.207413144776657</v>
+        <v>0.2074130727806035</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.7162277760684552</v>
+        <v>0.7162279295613433</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>0.8802486710270973</v>
+        <v>0.8802491213900754</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>-0.3371725334437184</v>
+        <v>-0.3371726482138072</v>
       </c>
       <c r="I26" s="17" t="n">
         <v>0</v>
@@ -2427,13 +3145,13 @@
       <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Active Rule / Implementation Summary</t>
         </is>
       </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="32" t="n"/>
+      <c r="B29" s="33" t="n"/>
+      <c r="C29" s="33" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
@@ -2472,7 +3190,7 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>equal_weight</t>
+          <t>sharpe_tilt</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -2581,12 +3299,12 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>No active rebalances have been executed yet.</t>
+          <t>Latest effective rebalance date. Average monthly turnover=2.1%.</t>
         </is>
       </c>
       <c r="D36" s="14" t="n"/>
@@ -2603,7 +3321,7 @@
         </is>
       </c>
       <c r="B37" s="24" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
@@ -2618,17 +3336,17 @@
       <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Factor / Regression Snapshot</t>
         </is>
       </c>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="32" t="n"/>
+      <c r="B38" s="33" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="8" t="n"/>
     </row>
@@ -2678,16 +3396,16 @@
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>0.0316350346175087</v>
+        <v>0.03163500163955029</v>
       </c>
       <c r="C40" s="21" t="n">
-        <v>1.064890557876907</v>
+        <v>1.064890883453683</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>0.8235779435905095</v>
+        <v>0.8235780804314634</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>83.84716818334908</v>
+        <v>83.84720766698554</v>
       </c>
       <c r="F40" s="26" t="n">
         <v>0</v>
@@ -2701,24 +3419,60 @@
       <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="16" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="26" t="n"/>
-      <c r="G41" s="18" t="n"/>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Revised Static Fund</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>0.02164288998715659</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>0.9872216861302682</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>0.8735519992489141</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>102.0001671248496</v>
+      </c>
+      <c r="F41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>latest rolling beta=0.85; proxy=benchmark_return; n=1508</t>
+        </is>
+      </c>
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="18" t="n"/>
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Revised Active Fund</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>0.02438337956065459</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>0.9661947118137731</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>0.8824308741621525</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>106.3178507695399</v>
+      </c>
+      <c r="F42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>latest rolling beta=0.76; proxy=benchmark_return; n=1508</t>
+        </is>
+      </c>
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="n"/>
     </row>
@@ -2745,18 +3499,18 @@
       <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>Scenario / Stress Snapshot</t>
         </is>
       </c>
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
-      <c r="H45" s="32" t="n"/>
+      <c r="B45" s="33" t="n"/>
+      <c r="C45" s="33" t="n"/>
+      <c r="D45" s="33" t="n"/>
+      <c r="E45" s="33" t="n"/>
+      <c r="F45" s="33" t="n"/>
+      <c r="G45" s="33" t="n"/>
+      <c r="H45" s="33" t="n"/>
       <c r="I45" s="8" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
@@ -2808,15 +3562,29 @@
           <t>Revised Static Fund</t>
         </is>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="16" t="inlineStr"/>
-      <c r="G47" s="17" t="n"/>
+      <c r="B47" s="17" t="n">
+        <v>0.1920325280450351</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>-0.1789012724756603</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>0.1651544991206367</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.6470241075079166</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>Worst 21-Day Window</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>-0.2606477903046253</v>
+      </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>Scenario/stress outputs are not ready yet.</t>
+          <t>Uses compounded selected-universe returns over the worst 21-day benchmark-proxy window.</t>
         </is>
       </c>
       <c r="I47" s="14" t="n"/>
@@ -2827,15 +3595,29 @@
           <t>Revised Active Fund</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="16" t="inlineStr"/>
-      <c r="G48" s="17" t="n"/>
+      <c r="B48" s="17" t="n">
+        <v>0.1995608752366695</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>-0.1650178054773065</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0.167962322171559</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.6680095974678362</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Worst 21-Day Window</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>-0.2581813390473018</v>
+      </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>Scenario/stress outputs are not ready yet.</t>
+          <t>Uses compounded selected-universe returns over the worst 21-day benchmark-proxy window.</t>
         </is>
       </c>
       <c r="I48" s="14" t="n"/>
@@ -2896,13 +3678,13 @@
       <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="31" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>Major Artifacts</t>
         </is>
       </c>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
+      <c r="B54" s="33" t="n"/>
+      <c r="C54" s="33" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
@@ -2964,12 +3746,12 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>fig_backtest_legacy_vs_benchmark.png</t>
+          <t>fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
+          <t>outputs/figures/fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="D57" s="14" t="n"/>
@@ -2987,12 +3769,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>fig_candidate_risk_return.png</t>
+          <t>fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_candidate_risk_return.png</t>
+          <t>outputs/figures/fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="D58" s="14" t="n"/>
@@ -3010,12 +3792,12 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>fig_revised_static_weights.png</t>
+          <t>fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_revised_static_weights.png</t>
+          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="D59" s="14" t="n"/>
@@ -3033,12 +3815,12 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>fig_factor_alpha_beta.png</t>
+          <t>fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_alpha_beta.png</t>
+          <t>outputs/figures/fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="D60" s="14" t="n"/>
@@ -3056,12 +3838,12 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>fig_factor_rolling_beta.png</t>
+          <t>fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_rolling_beta.png</t>
+          <t>outputs/figures/fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="D61" s="14" t="n"/>
@@ -3079,12 +3861,12 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>fig_scenario_monte_carlo_distribution.png</t>
+          <t>fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
+          <t>outputs/figures/fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="D62" s="14" t="n"/>
@@ -3102,12 +3884,12 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>fig_scenario_stress_impacts.png</t>
+          <t>fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
+          <t>outputs/figures/fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="D63" s="14" t="n"/>
@@ -3120,17 +3902,17 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>tbl_backtest_legacy_static_active_benchmark.csv</t>
+          <t>fig_factor_rolling_beta.png</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_backtest_legacy_static_active_benchmark.csv</t>
+          <t>outputs/figures/fig_factor_rolling_beta.png</t>
         </is>
       </c>
       <c r="D64" s="14" t="n"/>
@@ -3143,17 +3925,17 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>tbl_backtest_legacy_static_benchmark.csv</t>
+          <t>fig_scenario_monte_carlo_distribution.png</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_backtest_legacy_static_benchmark.csv</t>
+          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
         </is>
       </c>
       <c r="D65" s="14" t="n"/>
@@ -3166,17 +3948,17 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>tbl_backtest_legacy_vs_benchmark.csv</t>
+          <t>fig_scenario_stress_impacts.png</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_backtest_legacy_vs_benchmark.csv</t>
+          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
         </is>
       </c>
       <c r="D66" s="14" t="n"/>
@@ -3194,12 +3976,12 @@
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>tbl_factor_capm_summary.csv</t>
+          <t>tbl_backtest_legacy_static_active_benchmark.csv</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_factor_capm_summary.csv</t>
+          <t>outputs/tables/tbl_backtest_legacy_static_active_benchmark.csv</t>
         </is>
       </c>
       <c r="D67" s="14" t="n"/>
@@ -3217,12 +3999,12 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>tbl_scenario_stress_summary.csv</t>
+          <t>tbl_backtest_legacy_static_benchmark.csv</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
+          <t>outputs/tables/tbl_backtest_legacy_static_benchmark.csv</t>
         </is>
       </c>
       <c r="D68" s="14" t="n"/>
@@ -3240,12 +4022,12 @@
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>tbl_project_manifest.csv</t>
+          <t>tbl_backtest_legacy_vs_benchmark.csv</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_project_manifest.csv</t>
+          <t>outputs/tables/tbl_backtest_legacy_vs_benchmark.csv</t>
         </is>
       </c>
       <c r="D69" s="14" t="n"/>
@@ -3256,9 +4038,21 @@
       <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="16" t="n"/>
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="16" t="n"/>
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>tbl_factor_capm_summary.csv</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>outputs/tables/tbl_factor_capm_summary.csv</t>
+        </is>
+      </c>
       <c r="D70" s="14" t="n"/>
       <c r="E70" s="14" t="n"/>
       <c r="F70" s="14" t="n"/>
@@ -3267,9 +4061,21 @@
       <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="16" t="n"/>
-      <c r="B71" s="16" t="n"/>
-      <c r="C71" s="16" t="n"/>
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>tbl_scenario_stress_summary.csv</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
+        </is>
+      </c>
       <c r="D71" s="14" t="n"/>
       <c r="E71" s="14" t="n"/>
       <c r="F71" s="14" t="n"/>
@@ -3278,9 +4084,21 @@
       <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="16" t="n"/>
-      <c r="B72" s="16" t="n"/>
-      <c r="C72" s="16" t="n"/>
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>tbl_project_manifest.csv</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>outputs/tables/tbl_project_manifest.csv</t>
+        </is>
+      </c>
       <c r="D72" s="14" t="n"/>
       <c r="E72" s="14" t="n"/>
       <c r="F72" s="14" t="n"/>
@@ -3625,21 +4443,21 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10.83203125" customWidth="1" style="2" min="7" max="8"/>
-    <col width="10.83203125" customWidth="1" style="2" min="9" max="16384"/>
+    <col width="10.83203125" customWidth="1" style="2" min="7" max="12"/>
+    <col width="10.83203125" customWidth="1" style="2" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>Notes and Manifest</t>
         </is>
       </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
+      <c r="B1" s="33" t="n"/>
+      <c r="C1" s="33" t="n"/>
+      <c r="D1" s="33" t="n"/>
+      <c r="E1" s="33" t="n"/>
+      <c r="F1" s="33" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
@@ -3663,11 +4481,7 @@
           <t>known_issue_1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>No revised 2020 portfolio selections detected yet. Pipeline will default to the legacy fund summary.</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3720,7 +4534,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3730,12 +4544,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pipeline_20260417_095136.log</t>
+          <t>pipeline_20260424_105713.log</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>outputs/logs/pipeline_20260417_095136.log</t>
+          <t>outputs/logs/pipeline_20260424_105713.log</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3748,7 +4562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3776,7 +4590,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3804,7 +4618,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3832,7 +4646,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3860,7 +4674,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3888,7 +4702,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3916,7 +4730,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3944,7 +4758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3972,7 +4786,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4000,7 +4814,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4028,7 +4842,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4056,7 +4870,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4084,7 +4898,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4112,7 +4926,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4140,7 +4954,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4168,7 +4982,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4178,12 +4992,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>tbl_backtest_legacy_static_benchmark.csv</t>
+          <t>tbl_revised_static_weights_daily.csv</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_backtest_legacy_static_benchmark.csv</t>
+          <t>outputs/tables/tbl_revised_static_weights_daily.csv</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4196,7 +5010,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4206,12 +5020,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tbl_revised_active_daily.csv</t>
+          <t>tbl_revised_static_weights_snapshot.csv</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_revised_active_daily.csv</t>
+          <t>outputs/tables/tbl_revised_static_weights_snapshot.csv</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4224,7 +5038,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4234,12 +5048,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tbl_revised_active_weights_daily.csv</t>
+          <t>tbl_backtest_legacy_static_benchmark.csv</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_revised_active_weights_daily.csv</t>
+          <t>outputs/tables/tbl_backtest_legacy_static_benchmark.csv</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4252,7 +5066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4262,12 +5076,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tbl_revised_active_rebalance_log.csv</t>
+          <t>tbl_revised_active_daily.csv</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_revised_active_rebalance_log.csv</t>
+          <t>outputs/tables/tbl_revised_active_daily.csv</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4280,7 +5094,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4290,12 +5104,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tbl_backtest_legacy_static_active_benchmark.csv</t>
+          <t>tbl_revised_active_weights_daily.csv</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_backtest_legacy_static_active_benchmark.csv</t>
+          <t>outputs/tables/tbl_revised_active_weights_daily.csv</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4308,7 +5122,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4318,12 +5132,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tbl_factor_capm_summary.csv</t>
+          <t>tbl_revised_active_weights_snapshot.csv</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_factor_capm_summary.csv</t>
+          <t>outputs/tables/tbl_revised_active_weights_snapshot.csv</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4336,7 +5150,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4346,12 +5160,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tbl_factor_rolling_beta.csv</t>
+          <t>tbl_revised_active_rebalance_log.csv</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_factor_rolling_beta.csv</t>
+          <t>outputs/tables/tbl_revised_active_rebalance_log.csv</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4364,7 +5178,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4374,12 +5188,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tbl_scenario_monte_carlo_summary.csv</t>
+          <t>tbl_backtest_legacy_static_active_benchmark.csv</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_monte_carlo_summary.csv</t>
+          <t>outputs/tables/tbl_backtest_legacy_static_active_benchmark.csv</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4392,7 +5206,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,12 +5216,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>tbl_scenario_monte_carlo_draws.csv</t>
+          <t>tbl_factor_capm_summary.csv</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_monte_carlo_draws.csv</t>
+          <t>outputs/tables/tbl_factor_capm_summary.csv</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4420,7 +5234,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4430,12 +5244,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>tbl_scenario_stress_summary.csv</t>
+          <t>tbl_factor_rolling_beta.csv</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
+          <t>outputs/tables/tbl_factor_rolling_beta.csv</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4448,22 +5262,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>figure</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>fig_inherited_fund_overview.png</t>
+          <t>tbl_scenario_monte_carlo_summary.csv</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_fund_overview.png</t>
+          <t>outputs/tables/tbl_scenario_monte_carlo_summary.csv</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4476,22 +5290,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>figure</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fig_inherited_drawdown.png</t>
+          <t>tbl_scenario_monte_carlo_draws.csv</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_drawdown.png</t>
+          <t>outputs/tables/tbl_scenario_monte_carlo_draws.csv</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4504,22 +5318,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>figure</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fig_inherited_weights_snapshot.png</t>
+          <t>tbl_scenario_stress_summary.csv</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_weights_snapshot.png</t>
+          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4532,7 +5346,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4542,12 +5356,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>fig_backtest_legacy_vs_benchmark.png</t>
+          <t>fig_inherited_fund_overview.png</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
+          <t>outputs/figures/fig_inherited_fund_overview.png</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4560,7 +5374,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4570,12 +5384,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>fig_candidate_risk_return.png</t>
+          <t>fig_inherited_drawdown.png</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_candidate_risk_return.png</t>
+          <t>outputs/figures/fig_inherited_drawdown.png</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4588,7 +5402,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4598,12 +5412,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>fig_candidate_recent_return.png</t>
+          <t>fig_inherited_weights_snapshot.png</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_candidate_recent_return.png</t>
+          <t>outputs/figures/fig_inherited_weights_snapshot.png</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4616,7 +5430,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4626,12 +5440,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fig_revised_static_weights.png</t>
+          <t>fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_revised_static_weights.png</t>
+          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4644,7 +5458,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4654,12 +5468,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>fig_factor_alpha_beta.png</t>
+          <t>fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_alpha_beta.png</t>
+          <t>outputs/figures/fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4672,7 +5486,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4682,12 +5496,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>fig_factor_rolling_beta.png</t>
+          <t>fig_candidate_recent_return.png</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_rolling_beta.png</t>
+          <t>outputs/figures/fig_candidate_recent_return.png</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4700,7 +5514,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4710,12 +5524,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>fig_scenario_monte_carlo_distribution.png</t>
+          <t>fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
+          <t>outputs/figures/fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4728,7 +5542,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4738,12 +5552,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>fig_scenario_stress_impacts.png</t>
+          <t>fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
+          <t>outputs/figures/fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4756,22 +5570,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yf_prices_raw_20260417_095138.csv</t>
+          <t>fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>data/raw/yf_prices_raw_20260417_095138.csv</t>
+          <t>outputs/figures/fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4784,22 +5598,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>prices_adjclose_daily.csv</t>
+          <t>fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data/clean/prices_adjclose_daily.csv</t>
+          <t>outputs/figures/fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4812,22 +5626,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>returns_daily.csv</t>
+          <t>fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data/clean/returns_daily.csv</t>
+          <t>outputs/figures/fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4840,36 +5654,171 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-17 09:51:39</t>
+          <t>2026-04-24 10:57:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>figure</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fig_factor_rolling_beta.png</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>outputs/figures/fig_factor_rolling_beta.png</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-24 10:57:15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>figure</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>fig_scenario_monte_carlo_distribution.png</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-24 10:57:15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>figure</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>fig_scenario_stress_impacts.png</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-24 10:57:15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>table</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>prices_adjclose_daily.csv</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>data/clean/prices_adjclose_daily.csv</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-24 10:57:15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>returns_daily.csv</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>data/clean/returns_daily.csv</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-24 10:57:15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>tbl_project_manifest.csv</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>outputs/tables/tbl_project_manifest.csv</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>created</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-    </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
+      <c r="F66" t="inlineStr"/>
+    </row>
     <row r="67"/>
     <row r="68"/>
     <row r="69"/>

--- a/fund_manager_control.xlsx
+++ b/fund_manager_control.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="InheritedFund" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Candidates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Constraints" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Outputs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Notes_Manifest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InheritedFund" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constraints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes_Manifest" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -2620,7 +2620,7 @@
         <v>0.15</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>0.1471274389793825</v>
+        <v>0.1471274341940386</v>
       </c>
       <c r="G10" s="18" t="inlineStr"/>
       <c r="H10" s="14" t="n"/>
@@ -2651,7 +2651,7 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1508812989850544</v>
+        <v>0.1508812969171239</v>
       </c>
       <c r="G11" s="18" t="inlineStr"/>
       <c r="H11" s="14" t="n"/>
@@ -2682,7 +2682,7 @@
         <v>0.1</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>0.106404989268606</v>
+        <v>0.1064049878066885</v>
       </c>
       <c r="G12" s="18" t="inlineStr"/>
       <c r="H12" s="14" t="n"/>
@@ -2713,7 +2713,7 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>0.1017972584376416</v>
+        <v>0.1017972645565387</v>
       </c>
       <c r="G13" s="18" t="inlineStr"/>
       <c r="H13" s="14" t="n"/>
@@ -2744,7 +2744,7 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.1000609001022294</v>
+        <v>0.1000608996606066</v>
       </c>
       <c r="G14" s="18" t="inlineStr"/>
       <c r="H14" s="14" t="n"/>
@@ -2775,7 +2775,7 @@
         <v>0.08</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>0.08457226388181856</v>
+        <v>0.0845722635787395</v>
       </c>
       <c r="G15" s="18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>0.08</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>0.08393035349059123</v>
+        <v>0.08393035234305647</v>
       </c>
       <c r="G16" s="18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>0.08</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.07665445186007529</v>
+        <v>0.07665445080520156</v>
       </c>
       <c r="G17" s="18" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>0.08</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>0.07197041622530083</v>
+        <v>0.07197041523092031</v>
       </c>
       <c r="G18" s="18" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>0.08</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>0.07660062876930029</v>
+        <v>0.07660063490708581</v>
       </c>
       <c r="G19" s="18" t="inlineStr">
         <is>
@@ -3005,25 +3005,25 @@
         </is>
       </c>
       <c r="B23" s="20" t="n">
-        <v>15261596.96739008</v>
+        <v>15261595.36418564</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1.757094603014801</v>
+        <v>1.757094623343857</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>0.1846861989538795</v>
+        <v>0.1846862004135945</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.2432813945947335</v>
+        <v>0.2432814090253524</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.75914641668976</v>
+        <v>0.759146377659907</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>1.002197876885282</v>
+        <v>1.00219769134674</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>-0.3137782669699901</v>
+        <v>-0.3137782047937665</v>
       </c>
       <c r="I23" s="17" t="n">
         <v>0</v>
@@ -3036,25 +3036,25 @@
         </is>
       </c>
       <c r="B24" s="20" t="n">
-        <v>14048737.59742697</v>
+        <v>14048735.60588276</v>
       </c>
       <c r="C24" s="17" t="n">
-        <v>1.537984635015615</v>
+        <v>1.537984560556164</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>0.168405655926855</v>
+        <v>0.1684056501985822</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.2190818660371811</v>
+        <v>0.2190818779642209</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>0.76868824870368</v>
+        <v>0.7686881807087904</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>0.9819216569586509</v>
+        <v>0.9819214333872529</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>-0.273907482893831</v>
+        <v>-0.2739074727600548</v>
       </c>
       <c r="I24" s="17" t="n">
         <v>0</v>
@@ -3067,28 +3067,28 @@
         </is>
       </c>
       <c r="B25" s="20" t="n">
-        <v>14100074.20713302</v>
+        <v>14100072.57231949</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1.547258886580511</v>
+        <v>1.547258877609133</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>0.1691180541192125</v>
+        <v>0.1691180534311252</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.2133341758305466</v>
+        <v>0.2133341856893367</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>0.7927377479993858</v>
+        <v>0.7927377081392838</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>1.004152961658763</v>
+        <v>1.004152756535374</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>-0.27829229113173</v>
+        <v>-0.2782922855380526</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.02146566493433784</v>
+        <v>0.02146566611007893</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -3098,25 +3098,25 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>12679565.84077461</v>
+        <v>12679565.71866843</v>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1.290635942153882</v>
+        <v>1.290636177611779</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>0.1485550356816079</v>
+        <v>0.1485550554107491</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.2074130727806035</v>
+        <v>0.2074132215599161</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.7162279295613433</v>
+        <v>0.7162275109247824</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>0.8802491213900754</v>
+        <v>0.8802481899604394</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>-0.3371726482138072</v>
+        <v>-0.3371724347445537</v>
       </c>
       <c r="I26" s="17" t="n">
         <v>0</v>
@@ -3396,16 +3396,16 @@
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>0.03163500163955029</v>
+        <v>0.03163510732204888</v>
       </c>
       <c r="C40" s="21" t="n">
-        <v>1.064890883453683</v>
+        <v>1.064889855007011</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>0.8235780804314634</v>
+        <v>0.8235775789758242</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>83.84720766698554</v>
+        <v>83.84706297884148</v>
       </c>
       <c r="F40" s="26" t="n">
         <v>0</v>
@@ -3425,16 +3425,16 @@
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>0.02164288998715659</v>
+        <v>0.02164297517995462</v>
       </c>
       <c r="C41" s="21" t="n">
-        <v>0.9872216861302682</v>
+        <v>0.987220837293985</v>
       </c>
       <c r="D41" s="17" t="n">
-        <v>0.8735519992489141</v>
+        <v>0.8735516551467442</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>102.0001671248496</v>
+        <v>102.0000082494243</v>
       </c>
       <c r="F41" s="26" t="n">
         <v>0</v>
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>0.02438337956065459</v>
+        <v>0.02438345812577851</v>
       </c>
       <c r="C42" s="21" t="n">
-        <v>0.9661947118137731</v>
+        <v>0.9661939346704905</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>0.8824308741621525</v>
+        <v>0.8824306390150648</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>106.3178507695399</v>
+        <v>106.3177302822624</v>
       </c>
       <c r="F42" s="26" t="n">
         <v>0</v>
@@ -3563,16 +3563,16 @@
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>0.1920325280450351</v>
+        <v>0.1920325283000659</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>-0.1789012724756603</v>
+        <v>-0.1789011948294551</v>
       </c>
       <c r="D47" s="17" t="n">
-        <v>0.1651544991206367</v>
+        <v>0.1651545909680865</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>0.6470241075079166</v>
+        <v>0.6470243636000705</v>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>-0.2606477903046253</v>
+        <v>-0.2606477447179319</v>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
@@ -3596,16 +3596,16 @@
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>0.1995608752366695</v>
+        <v>0.1995608800675977</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>-0.1650178054773065</v>
+        <v>-0.165017650650727</v>
       </c>
       <c r="D48" s="17" t="n">
-        <v>0.167962322171559</v>
+        <v>0.1679622681627537</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.6680095974678362</v>
+        <v>0.6680097158352258</v>
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>-0.2581813390473018</v>
+        <v>-0.2581812969390676</v>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pipeline_20260424_105713.log</t>
+          <t>pipeline_20260502_183714.log</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>outputs/logs/pipeline_20260424_105713.log</t>
+          <t>outputs/logs/pipeline_20260502_183714.log</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4562,7 +4562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4590,7 +4590,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4674,7 +4674,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4702,7 +4702,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4814,7 +4814,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4842,7 +4842,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4898,7 +4898,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5038,7 +5038,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5150,7 +5150,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5178,7 +5178,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5234,7 +5234,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>tbl_scenario_monte_carlo_summary.csv</t>
+          <t>tbl_factor_ff3_summary.csv</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_monte_carlo_summary.csv</t>
+          <t>outputs/tables/tbl_factor_ff3_summary.csv</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5290,7 +5290,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tbl_scenario_monte_carlo_draws.csv</t>
+          <t>tbl_scenario_monte_carlo_summary.csv</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_monte_carlo_draws.csv</t>
+          <t>outputs/tables/tbl_scenario_monte_carlo_summary.csv</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>tbl_scenario_stress_summary.csv</t>
+          <t>tbl_scenario_monte_carlo_draws.csv</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
+          <t>outputs/tables/tbl_scenario_monte_carlo_draws.csv</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5346,22 +5346,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>figure</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>fig_inherited_fund_overview.png</t>
+          <t>tbl_scenario_stress_summary.csv</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_fund_overview.png</t>
+          <t>outputs/tables/tbl_scenario_stress_summary.csv</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>fig_inherited_drawdown.png</t>
+          <t>fig_inherited_fund_overview.png</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_drawdown.png</t>
+          <t>outputs/figures/fig_inherited_fund_overview.png</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>fig_inherited_weights_snapshot.png</t>
+          <t>fig_inherited_drawdown.png</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_inherited_weights_snapshot.png</t>
+          <t>outputs/figures/fig_inherited_drawdown.png</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5430,7 +5430,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fig_backtest_legacy_vs_benchmark.png</t>
+          <t>fig_inherited_weights_snapshot.png</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
+          <t>outputs/figures/fig_inherited_weights_snapshot.png</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>fig_candidate_risk_return.png</t>
+          <t>fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_candidate_risk_return.png</t>
+          <t>outputs/figures/fig_backtest_legacy_vs_benchmark.png</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>fig_candidate_recent_return.png</t>
+          <t>fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_candidate_recent_return.png</t>
+          <t>outputs/figures/fig_candidate_risk_return.png</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5514,7 +5514,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>fig_revised_static_weights.png</t>
+          <t>fig_candidate_recent_return.png</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_revised_static_weights.png</t>
+          <t>outputs/figures/fig_candidate_recent_return.png</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>fig_legacy_static_benchmark.png</t>
+          <t>fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_legacy_static_benchmark.png</t>
+          <t>outputs/figures/fig_revised_static_weights.png</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5570,7 +5570,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>fig_revised_active_weights.png</t>
+          <t>fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_revised_active_weights.png</t>
+          <t>outputs/figures/fig_legacy_static_benchmark.png</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5598,7 +5598,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>fig_legacy_static_active_benchmark.png</t>
+          <t>fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_legacy_static_active_benchmark.png</t>
+          <t>outputs/figures/fig_revised_active_weights.png</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>fig_factor_alpha_beta.png</t>
+          <t>fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_alpha_beta.png</t>
+          <t>outputs/figures/fig_legacy_static_active_benchmark.png</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5654,7 +5654,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fig_factor_rolling_beta.png</t>
+          <t>fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_factor_rolling_beta.png</t>
+          <t>outputs/figures/fig_factor_alpha_beta.png</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>fig_scenario_monte_carlo_distribution.png</t>
+          <t>fig_factor_rolling_beta.png</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
+          <t>outputs/figures/fig_factor_rolling_beta.png</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>fig_scenario_stress_impacts.png</t>
+          <t>fig_factor_ff3.png</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
+          <t>outputs/figures/fig_factor_ff3.png</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5738,22 +5738,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>prices_adjclose_daily.csv</t>
+          <t>fig_scenario_monte_carlo_distribution.png</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>data/clean/prices_adjclose_daily.csv</t>
+          <t>outputs/figures/fig_scenario_monte_carlo_distribution.png</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5766,22 +5766,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>figure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>returns_daily.csv</t>
+          <t>fig_scenario_stress_impacts.png</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>data/clean/returns_daily.csv</t>
+          <t>outputs/figures/fig_scenario_stress_impacts.png</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5794,7 +5794,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-24 10:57:15</t>
+          <t>2026-05-02 18:37:22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5804,24 +5804,105 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>yf_prices_raw_20260502_183719.csv</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>data/raw/yf_prices_raw_20260502_183719.csv</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:37:22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>prices_adjclose_daily.csv</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>data/clean/prices_adjclose_daily.csv</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:37:22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>returns_daily.csv</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>data/clean/returns_daily.csv</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-02 18:37:22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>tbl_project_manifest.csv</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>outputs/tables/tbl_project_manifest.csv</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>created</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-    </row>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
+      <c r="F69" t="inlineStr"/>
+    </row>
     <row r="70"/>
     <row r="71"/>
     <row r="72"/>
